--- a/step_1/чек-лист проверок для функциональности поиска товаров на платформе shop.megafon.ru.xlsx
+++ b/step_1/чек-лист проверок для функциональности поиска товаров на платформе shop.megafon.ru.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Поиск по ключевому слову</t>
   </si>
   <si>
-    <t>Поиск по первой букве слова</t>
+    <t>Поиск по первым 3 буквам слова</t>
   </si>
   <si>
     <t>Товары найдены</t>
@@ -64,22 +64,16 @@
     <t>Автозаполнение выполняется</t>
   </si>
   <si>
-    <t>Поиск нажатием на кнопку "Все товары"</t>
+    <t>Поиск нажатием на "Enter"</t>
   </si>
   <si>
     <t>Поиск выполняется</t>
   </si>
   <si>
-    <t>Поиск нажатием на "Enter"</t>
-  </si>
-  <si>
     <t>Очистка поля нажатием на "крестик"</t>
   </si>
   <si>
     <t>Поле очищается</t>
-  </si>
-  <si>
-    <t>Очистка поля поиска, нажатием на кноопку "Очистить"</t>
   </si>
   <si>
     <t>Вставка текста в строку поиска "Ctrl + v"</t>
@@ -283,13 +277,13 @@
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
@@ -627,7 +621,7 @@
       <c r="A10" s="6">
         <v>8.0</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -660,10 +654,10 @@
       <c r="D12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="6">
+      <c r="A13" s="8">
         <v>11.0</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -672,14 +666,14 @@
       <c r="D13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="6">
+      <c r="A14" s="9">
         <v>12.0</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>18</v>
+      <c r="C14" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="4"/>
     </row>
@@ -687,11 +681,11 @@
       <c r="A15" s="8">
         <v>13.0</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -699,59 +693,59 @@
       <c r="A16" s="8">
         <v>14.0</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>21</v>
+      <c r="B16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="10">
+      <c r="A17" s="8">
         <v>15.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D17" s="4"/>
     </row>
     <row r="18">
-      <c r="A18" s="10">
+      <c r="A18" s="8">
         <v>16.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>17.0</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>18</v>
+      <c r="B19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="D19" s="4"/>
     </row>
     <row r="20">
-      <c r="A20" s="10">
+      <c r="A20" s="8">
         <v>18.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="4"/>
     </row>
@@ -759,189 +753,165 @@
       <c r="A21" s="8">
         <v>19.0</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="B21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="4"/>
     </row>
     <row r="22">
-      <c r="A22" s="10">
+      <c r="A22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8">
         <v>20.0</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10">
-        <v>21.0</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="4"/>
+      <c r="A24" s="8">
+        <v>21.0</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="6">
-        <v>21.0</v>
+      <c r="A25" s="8">
+        <v>22.0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6">
-        <v>22.0</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>40</v>
+      <c r="A26" s="8">
+        <v>23.0</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6">
-        <v>23.0</v>
+      <c r="A27" s="8">
+        <v>24.0</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6">
-        <v>24.0</v>
+      <c r="A28" s="8">
+        <v>25.0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6">
-        <v>25.0</v>
+      <c r="A29" s="8">
+        <v>26.0</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6">
-        <v>26.0</v>
-      </c>
-      <c r="B30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="D30" s="4"/>
     </row>
     <row r="31">
-      <c r="A31" s="6">
+      <c r="A31" s="13">
         <v>27.0</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="14" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>49</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D31" s="4"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="13">
+        <v>28.0</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="13">
-        <v>28.0</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>53</v>
+        <v>29.0</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D33" s="4"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="13">
-        <v>29.0</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="13">
-        <v>30.0</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A30:C30"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/step_1/чек-лист проверок для функциональности поиска товаров на платформе shop.megafon.ru.xlsx
+++ b/step_1/чек-лист проверок для функциональности поиска товаров на платформе shop.megafon.ru.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="630" yWindow="570" windowWidth="15975" windowHeight="7620"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -49,9 +52,6 @@
     <t>Поиск по ключевому слову</t>
   </si>
   <si>
-    <t>Поиск по первым 3 буквам слова</t>
-  </si>
-  <si>
     <t>Товары найдены</t>
   </si>
   <si>
@@ -176,41 +176,51 @@
   </si>
   <si>
     <t>Работоспособность в Opera</t>
+  </si>
+  <si>
+    <t>Поиск по первщй букве</t>
+  </si>
+  <si>
+    <t>Поиск нажатием на кнопку "Все товары"</t>
+  </si>
+  <si>
+    <t>Очистка поля нажатием на "Очистить"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF0F1119"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -230,9 +240,27 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -246,71 +274,65 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -500,22 +522,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.63"/>
-    <col customWidth="1" min="2" max="2" width="49.0"/>
-    <col customWidth="1" min="3" max="3" width="38.25"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="58.28515625" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,15 +552,17 @@
       </c>
       <c r="D1" s="4"/>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>1.0</v>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>4</v>
@@ -545,9 +572,9 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>2.0</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
@@ -557,9 +584,9 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>3.0</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
@@ -569,9 +596,9 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>4.0</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>8</v>
@@ -581,9 +608,9 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>5.0</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>9</v>
@@ -593,9 +620,9 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>6.0</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>10</v>
@@ -605,9 +632,9 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>7.0</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>11</v>
@@ -617,302 +644,330 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="B15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
+        <v>14</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="B17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8">
-        <v>11.0</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="B18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="B19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <v>18</v>
       </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9">
-        <v>12.0</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
         <v>19</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B21" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
         <v>20</v>
       </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8">
-        <v>13.0</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="B22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
         <v>21</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="B23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
         <v>22</v>
       </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8">
-        <v>14.0</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="B25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
         <v>23</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="B26" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="7">
         <v>24</v>
       </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8">
-        <v>15.0</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="B27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="7">
         <v>25</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8">
-        <v>16.0</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="B28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="7">
         <v>26</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="B29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="7">
         <v>27</v>
       </c>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9">
-        <v>17.0</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="B30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="7">
         <v>28</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="B31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="12">
         <v>29</v>
       </c>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8">
-        <v>18.0</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="B33" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A34" s="12">
         <v>30</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="B34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A35" s="12">
         <v>31</v>
       </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8">
-        <v>19.0</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8">
-        <v>20.0</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8">
-        <v>21.0</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8">
-        <v>22.0</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8">
-        <v>23.0</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8">
-        <v>24.0</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8">
-        <v>25.0</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8">
-        <v>26.0</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13">
-        <v>27.0</v>
-      </c>
-      <c r="B31" s="14" t="s">
+      <c r="B35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13">
-        <v>28.0</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="13">
-        <v>29.0</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="4"/>
+      <c r="D35" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A32:C32"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/step_1/чек-лист проверок для функциональности поиска товаров на платформе shop.megafon.ru.xlsx
+++ b/step_1/чек-лист проверок для функциональности поиска товаров на платформе shop.megafon.ru.xlsx
@@ -178,13 +178,13 @@
     <t>Работоспособность в Opera</t>
   </si>
   <si>
-    <t>Поиск по первщй букве</t>
-  </si>
-  <si>
     <t>Поиск нажатием на кнопку "Все товары"</t>
   </si>
   <si>
     <t>Очистка поля нажатием на "Очистить"</t>
+  </si>
+  <si>
+    <t>Поиск по первой букве</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
       </c>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>3</v>
       </c>
@@ -560,7 +560,7 @@
       <c r="C2" s="15"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -572,7 +572,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -584,7 +584,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -596,7 +596,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -608,7 +608,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -620,7 +620,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -644,19 +644,19 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -680,19 +680,19 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>12</v>
       </c>
@@ -704,19 +704,19 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>14</v>
       </c>
@@ -728,7 +728,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>15</v>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>16</v>
       </c>
@@ -752,7 +752,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
       </c>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>18</v>
       </c>
@@ -776,7 +776,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>19</v>
       </c>
@@ -788,7 +788,7 @@
       </c>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>20</v>
       </c>
@@ -800,7 +800,7 @@
       </c>
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>21</v>
       </c>
@@ -812,7 +812,7 @@
       </c>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
         <v>32</v>
       </c>
@@ -820,7 +820,7 @@
       <c r="C24" s="15"/>
       <c r="D24" s="4"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>22</v>
       </c>
@@ -834,7 +834,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>23</v>
       </c>
@@ -848,7 +848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>24</v>
       </c>
@@ -862,7 +862,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>25</v>
       </c>
